--- a/data/trans_orig/P19C05-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P19C05-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis en 2007</t>
+          <t>Población según si el motivo por su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis en 2007 (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23187</t>
+          <t>25318</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46175</t>
+          <t>45946</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22123</t>
+          <t>20979</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43637</t>
+          <t>42141</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>52056</t>
+          <t>51835</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>83296</t>
+          <t>82331</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>20,96%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>145318</t>
+          <t>145547</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>168306</t>
+          <t>166175</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>76,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>86,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>157585</t>
+          <t>159081</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>179099</t>
+          <t>180243</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>79,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>309420</t>
+          <t>310385</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>340660</t>
+          <t>340881</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>86,8%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45018</t>
+          <t>43562</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>74885</t>
+          <t>75284</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>46456</t>
+          <t>45679</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>75254</t>
+          <t>73595</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>97550</t>
+          <t>98842</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>136998</t>
+          <t>141046</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,57%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>334871</t>
+          <t>334472</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>364738</t>
+          <t>366194</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>81,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>365947</t>
+          <t>367606</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>394745</t>
+          <t>395522</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>713959</t>
+          <t>709911</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>753407</t>
+          <t>752115</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,38%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21798</t>
+          <t>22593</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42359</t>
+          <t>42346</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>53576</t>
+          <t>55144</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>83231</t>
+          <t>82655</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>82379</t>
+          <t>80362</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>117057</t>
+          <t>117667</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,4%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>194178</t>
+          <t>194191</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>214739</t>
+          <t>213944</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>205575</t>
+          <t>206151</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>235230</t>
+          <t>233662</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,18%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>408286</t>
+          <t>407676</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>442964</t>
+          <t>444981</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,72%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>84,7%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>33032</t>
+          <t>32406</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>56252</t>
+          <t>56069</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>54225</t>
+          <t>53617</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>81382</t>
+          <t>82241</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>93546</t>
+          <t>93595</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>131585</t>
+          <t>130775</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,06%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>211279</t>
+          <t>211462</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>234499</t>
+          <t>235125</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>218152</t>
+          <t>217293</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>245309</t>
+          <t>245917</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>72,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>435480</t>
+          <t>436290</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>473519</t>
+          <t>473470</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>76,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>83,49%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8688</t>
+          <t>8557</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22623</t>
+          <t>23024</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14911</t>
+          <t>15696</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32570</t>
+          <t>33399</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>27791</t>
+          <t>27925</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>49254</t>
+          <t>51695</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>15,02%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>147655</t>
+          <t>147254</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>161590</t>
+          <t>161721</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>141336</t>
+          <t>140507</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>158995</t>
+          <t>158210</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>80,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>294930</t>
+          <t>292489</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>316393</t>
+          <t>316259</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,89%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>27878</t>
+          <t>27186</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>48583</t>
+          <t>47159</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>22939</t>
+          <t>23482</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>43517</t>
+          <t>44253</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>53747</t>
+          <t>55285</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>85261</t>
+          <t>84982</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,58%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>140687</t>
+          <t>142111</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>161392</t>
+          <t>162084</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>75,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>160971</t>
+          <t>160235</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>181549</t>
+          <t>181006</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>78,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>308497</t>
+          <t>308776</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>340011</t>
+          <t>338473</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,35%</t>
+          <t>78,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>85,96%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>56705</t>
+          <t>56844</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>87753</t>
+          <t>88664</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,47 +2806,47 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
+          <t>12,24%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>19,1%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>82035</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>65839</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>100344</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>15,21%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
           <t>12,21%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>18,9%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>82035</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>65813</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>100463</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>15,21%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>12,2%</t>
-        </is>
-      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>131583</t>
+          <t>132203</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>176480</t>
+          <t>179212</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,86%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>376572</t>
+          <t>375661</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>407620</t>
+          <t>407481</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,49 +2919,49 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>81,1%</t>
+          <t>80,9%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
+          <t>87,76%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>444</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>457333</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>439024</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>473529</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>84,79%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>81,4%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
           <t>87,79%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>444</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>457333</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>438905</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>473555</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>84,79%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>81,37%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>87,8%</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>827</t>
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>827212</t>
+          <t>824480</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>872109</t>
+          <t>871489</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>86,83%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>31919</t>
+          <t>31511</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>56934</t>
+          <t>58281</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>63376</t>
+          <t>63471</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>97380</t>
+          <t>96882</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>102254</t>
+          <t>101670</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>143977</t>
+          <t>144530</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,93%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>468618</t>
+          <t>467271</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>493633</t>
+          <t>494041</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>495032</t>
+          <t>495530</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>529036</t>
+          <t>528941</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>973986</t>
+          <t>973433</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1015709</t>
+          <t>1016293</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>87,07%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>90,91%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>301710</t>
+          <t>303299</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>365333</t>
+          <t>369199</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>404636</t>
+          <t>406123</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>484194</t>
+          <t>483010</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>729461</t>
+          <t>726894</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>831117</t>
+          <t>827500</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,93%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2089409</t>
+          <t>2085543</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2153032</t>
+          <t>2151443</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2256743</t>
+          <t>2257927</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2336301</t>
+          <t>2334814</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>82,38%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4364562</t>
+          <t>4368179</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4466218</t>
+          <t>4468785</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>86,01%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis en 2012</t>
+          <t>Población según si el motivo por su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis en 2012 (tasa de respuesta: 99,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27690</t>
+          <t>26987</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>52860</t>
+          <t>52426</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28336</t>
+          <t>28405</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>51353</t>
+          <t>51322</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>61115</t>
+          <t>60452</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>96265</t>
+          <t>96555</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,32%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>197700</t>
+          <t>198134</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>222870</t>
+          <t>223573</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,9%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>197886</t>
+          <t>197917</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>220903</t>
+          <t>220834</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>79,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>403535</t>
+          <t>403245</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>438685</t>
+          <t>439348</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,9%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34149</t>
+          <t>33768</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>61085</t>
+          <t>62876</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>53966</t>
+          <t>54294</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>86751</t>
+          <t>86455</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>96558</t>
+          <t>98112</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>138823</t>
+          <t>139717</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,55%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>345245</t>
+          <t>343454</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>372181</t>
+          <t>372562</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>351072</t>
+          <t>351368</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>383857</t>
+          <t>383529</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>80,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>705330</t>
+          <t>704436</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>747595</t>
+          <t>746041</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>83,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>88,38%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>37422</t>
+          <t>37367</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>62518</t>
+          <t>64163</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>60126</t>
+          <t>61082</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>93249</t>
+          <t>92690</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>105839</t>
+          <t>105124</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>145624</t>
+          <t>145955</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,45%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>231146</t>
+          <t>229501</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>256242</t>
+          <t>256297</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>235503</t>
+          <t>236062</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>268626</t>
+          <t>267670</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,64%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>476792</t>
+          <t>476461</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>516577</t>
+          <t>517292</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>76,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>83,11%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>32781</t>
+          <t>33884</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>60369</t>
+          <t>58325</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>47110</t>
+          <t>46855</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>74831</t>
+          <t>75296</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>85982</t>
+          <t>85638</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>126017</t>
+          <t>122558</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>18,69%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>252708</t>
+          <t>254752</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>280296</t>
+          <t>279193</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>81,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>267984</t>
+          <t>267519</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>295705</t>
+          <t>295960</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>529874</t>
+          <t>533333</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>569909</t>
+          <t>570253</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,79%</t>
+          <t>81,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>86,94%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23659</t>
+          <t>23303</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>45690</t>
+          <t>46551</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>25030</t>
+          <t>23901</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>45427</t>
+          <t>45844</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>53537</t>
+          <t>54006</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>83508</t>
+          <t>84468</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,85%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>146368</t>
+          <t>145507</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>168399</t>
+          <t>168755</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,21%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>149155</t>
+          <t>148738</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>169552</t>
+          <t>170681</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,65%</t>
+          <t>76,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>303132</t>
+          <t>302172</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>333103</t>
+          <t>332634</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>86,03%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19369</t>
+          <t>20337</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>39864</t>
+          <t>39843</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>42341</t>
+          <t>40064</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>69809</t>
+          <t>67464</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>68280</t>
+          <t>69020</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>101756</t>
+          <t>101481</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,71%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>210109</t>
+          <t>210130</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>230604</t>
+          <t>229636</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>195021</t>
+          <t>197366</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>222489</t>
+          <t>224766</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>74,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>413047</t>
+          <t>413322</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>446523</t>
+          <t>445783</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>80,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>86,59%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>93047</t>
+          <t>94749</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>134688</t>
+          <t>136249</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>111958</t>
+          <t>110637</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>154076</t>
+          <t>153097</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>219121</t>
+          <t>217591</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>278074</t>
+          <t>275236</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>22,92%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>440403</t>
+          <t>438842</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>482044</t>
+          <t>480342</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>76,31%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>471911</t>
+          <t>472890</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>514029</t>
+          <t>515350</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>75,39%</t>
+          <t>75,54%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>923004</t>
+          <t>925842</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>981957</t>
+          <t>983487</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>77,08%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>81,88%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>64588</t>
+          <t>64664</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>101701</t>
+          <t>100117</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>91781</t>
+          <t>91854</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>131383</t>
+          <t>130798</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>166883</t>
+          <t>164690</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>221239</t>
+          <t>219077</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,4%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>532204</t>
+          <t>533788</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>569317</t>
+          <t>569241</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>570911</t>
+          <t>571496</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>610513</t>
+          <t>610440</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>86,92%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1114960</t>
+          <t>1117122</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1169316</t>
+          <t>1171509</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>87,67%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>397309</t>
+          <t>400015</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>481554</t>
+          <t>479745</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>528109</t>
+          <t>529515</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>617858</t>
+          <t>620549</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>950909</t>
+          <t>952121</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1076018</t>
+          <t>1068420</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,63%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2433105</t>
+          <t>2434914</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2517350</t>
+          <t>2514644</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>83,54%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2528463</t>
+          <t>2525772</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2618212</t>
+          <t>2616806</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>80,28%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4984962</t>
+          <t>4992560</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5110071</t>
+          <t>5108859</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>84,29%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis en 2016</t>
+          <t>Población según si el motivo por su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6825</t>
+          <t>6814</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21867</t>
+          <t>20996</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12528</t>
+          <t>11959</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30173</t>
+          <t>29337</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22230</t>
+          <t>21578</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44588</t>
+          <t>46879</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,54%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>223351</t>
+          <t>224222</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>238393</t>
+          <t>238404</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>216161</t>
+          <t>216997</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>233806</t>
+          <t>234375</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>446963</t>
+          <t>444672</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>469321</t>
+          <t>469973</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,61%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36582</t>
+          <t>38289</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>64943</t>
+          <t>64477</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>44757</t>
+          <t>45913</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>74941</t>
+          <t>75035</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>88850</t>
+          <t>89555</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>129468</t>
+          <t>128028</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>16,92%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>298222</t>
+          <t>298688</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>326583</t>
+          <t>324876</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>82,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>318386</t>
+          <t>318292</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>348570</t>
+          <t>347414</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>627024</t>
+          <t>628464</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>667642</t>
+          <t>666937</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>83,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>88,16%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23378</t>
+          <t>21326</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>43742</t>
+          <t>43411</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21407</t>
+          <t>20648</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42399</t>
+          <t>42662</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>48230</t>
+          <t>49009</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>78397</t>
+          <t>80376</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,43%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>246765</t>
+          <t>247096</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>267129</t>
+          <t>269181</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>85,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>265365</t>
+          <t>265102</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>286357</t>
+          <t>287116</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>519873</t>
+          <t>517894</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>550040</t>
+          <t>549261</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>91,81%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31690</t>
+          <t>31697</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>55873</t>
+          <t>57502</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8428,7 +8428,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>41546</t>
+          <t>42738</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>71065</t>
+          <t>73243</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>83031</t>
+          <t>81913</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>122139</t>
+          <t>120472</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,74%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>274174</t>
+          <t>272545</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>298357</t>
+          <t>298350</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>277796</t>
+          <t>275618</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>307315</t>
+          <t>306123</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>556769</t>
+          <t>558436</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>595877</t>
+          <t>596995</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>82,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,93%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10681</t>
+          <t>10600</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26425</t>
+          <t>26471</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17507</t>
+          <t>17184</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>36206</t>
+          <t>34733</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,47 +8801,47 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
+          <t>11,81%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>23,87%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>42682</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>31856</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>57117</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>16,12%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>12,03%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>24,88%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>42682</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>31961</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>55393</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>16,12%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>12,07%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>21,58%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>92797</t>
+          <t>92751</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>108541</t>
+          <t>108622</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>77,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>109294</t>
+          <t>110767</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>127993</t>
+          <t>128316</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,47 +8914,47 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>76,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
+          <t>88,19%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>222040</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>207605</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>232866</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>83,88%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>78,42%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
           <t>87,97%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>222040</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>209329</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>232761</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>83,88%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>79,08%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>87,93%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10738</t>
+          <t>10284</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27267</t>
+          <t>25575</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8911</t>
+          <t>9273</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>25519</t>
+          <t>26048</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>22957</t>
+          <t>23268</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>45109</t>
+          <t>46053</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,58%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>206348</t>
+          <t>208040</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>222877</t>
+          <t>223331</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>221618</t>
+          <t>221089</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>238226</t>
+          <t>237864</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>435644</t>
+          <t>434700</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>457796</t>
+          <t>457485</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,16%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25865</t>
+          <t>25931</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>50106</t>
+          <t>50841</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>31584</t>
+          <t>32312</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>57372</t>
+          <t>57707</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>63543</t>
+          <t>62265</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>99589</t>
+          <t>98417</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,59%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>392201</t>
+          <t>391466</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>416442</t>
+          <t>416376</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>429679</t>
+          <t>429344</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>455467</t>
+          <t>454739</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>829769</t>
+          <t>830941</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>865815</t>
+          <t>867093</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,3%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>60773</t>
+          <t>60380</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>95793</t>
+          <t>93776</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>66273</t>
+          <t>66913</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>102249</t>
+          <t>103872</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>135796</t>
+          <t>134326</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>184505</t>
+          <t>185021</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,89%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>544459</t>
+          <t>546476</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>579479</t>
+          <t>579872</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>589092</t>
+          <t>587469</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>625068</t>
+          <t>624428</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1147088</t>
+          <t>1146572</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1195797</t>
+          <t>1197267</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>89,91%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>251292</t>
+          <t>253386</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>316354</t>
+          <t>318699</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>299632</t>
+          <t>296557</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>371248</t>
+          <t>369711</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>571410</t>
+          <t>570141</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>669867</t>
+          <t>667864</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,07%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2347979</t>
+          <t>2345634</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2413041</t>
+          <t>2410947</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2496067</t>
+          <t>2497604</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2567683</t>
+          <t>2570758</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4861781</t>
+          <t>4863784</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4960238</t>
+          <t>4961507</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,69%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis en 2023</t>
+          <t>Población según si el motivo por su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis en 2023 (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20776</t>
+          <t>20615</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40431</t>
+          <t>41271</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16245</t>
+          <t>16786</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31424</t>
+          <t>30673</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>40530</t>
+          <t>40552</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>65397</t>
+          <t>64744</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,92%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>264999</t>
+          <t>264159</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>284654</t>
+          <t>284815</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>256183</t>
+          <t>256934</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>271362</t>
+          <t>270821</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>527640</t>
+          <t>528293</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>552507</t>
+          <t>552485</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,16%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27353</t>
+          <t>27656</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>52299</t>
+          <t>51814</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>53720</t>
+          <t>54744</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>78281</t>
+          <t>78072</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>88546</t>
+          <t>87761</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>122579</t>
+          <t>122800</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,18%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>454685</t>
+          <t>455170</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>479631</t>
+          <t>479328</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>423267</t>
+          <t>423476</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>447828</t>
+          <t>446804</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>84,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>885953</t>
+          <t>885732</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>919986</t>
+          <t>920771</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,3%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25889</t>
+          <t>26096</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44076</t>
+          <t>44119</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>39478</t>
+          <t>39827</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59261</t>
+          <t>59434</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>71321</t>
+          <t>70490</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>97270</t>
+          <t>98076</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,41%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>257116</t>
+          <t>257073</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>275303</t>
+          <t>275096</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>276014</t>
+          <t>275841</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>295797</t>
+          <t>295448</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>539197</t>
+          <t>538391</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>565146</t>
+          <t>565977</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>84,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>88,92%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28000</t>
+          <t>28013</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50391</t>
+          <t>51095</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11751,7 +11751,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28843</t>
+          <t>30828</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>64696</t>
+          <t>63910</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>60637</t>
+          <t>64561</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>105289</t>
+          <t>106518</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,59%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>259729</t>
+          <t>259025</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>282120</t>
+          <t>282107</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>408769</t>
+          <t>409555</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>444622</t>
+          <t>442637</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>678296</t>
+          <t>677067</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>722948</t>
+          <t>719024</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>91,76%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13646</t>
+          <t>13370</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26854</t>
+          <t>25537</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>36165</t>
+          <t>36102</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>50291</t>
+          <t>50363</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>53291</t>
+          <t>52390</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>71585</t>
+          <t>73062</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,71%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>141575</t>
+          <t>142892</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>154783</t>
+          <t>155059</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>152001</t>
+          <t>151929</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>166127</t>
+          <t>166190</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>75,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>82,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>299136</t>
+          <t>297659</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>317430</t>
+          <t>318331</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>80,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>85,87%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>24781</t>
+          <t>25156</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>40736</t>
+          <t>41267</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21217</t>
+          <t>21587</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>35310</t>
+          <t>34847</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>50296</t>
+          <t>48941</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>70397</t>
+          <t>70617</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,12%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>212996</t>
+          <t>212465</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>228951</t>
+          <t>228576</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>211040</t>
+          <t>211503</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>225133</t>
+          <t>224763</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>429685</t>
+          <t>429465</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>449786</t>
+          <t>451141</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>90,21%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>60017</t>
+          <t>59384</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>94345</t>
+          <t>94391</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>32732</t>
+          <t>32434</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>106422</t>
+          <t>105539</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>97093</t>
+          <t>87121</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>185436</t>
+          <t>187095</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,1%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>505350</t>
+          <t>505304</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>539678</t>
+          <t>540311</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>721943</t>
+          <t>722826</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>795633</t>
+          <t>795931</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1242624</t>
+          <t>1240965</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1330967</t>
+          <t>1340939</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,9%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>21257</t>
+          <t>25395</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>79422</t>
+          <t>78796</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>54723</t>
+          <t>54867</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>78107</t>
+          <t>79113</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>72784</t>
+          <t>74538</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>150426</t>
+          <t>148241</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,19%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>829217</t>
+          <t>829843</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>887382</t>
+          <t>883244</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>625817</t>
+          <t>624811</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>649201</t>
+          <t>649057</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1462137</t>
+          <t>1464322</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1539779</t>
+          <t>1538025</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,38%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>244798</t>
+          <t>247443</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>361711</t>
+          <t>360860</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>312993</t>
+          <t>326155</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>437865</t>
+          <t>438160</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>620979</t>
+          <t>622322</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>785501</t>
+          <t>779952</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,25%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2992510</t>
+          <t>2993361</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3109423</t>
+          <t>3106778</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3140962</t>
+          <t>3140667</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3265834</t>
+          <t>3252672</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6147547</t>
+          <t>6153096</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6312069</t>
+          <t>6310726</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>91,02%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P19C05-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P19C05-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25318</t>
+          <t>25370</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>45946</t>
+          <t>45401</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20979</t>
+          <t>22081</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42141</t>
+          <t>42183</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>51835</t>
+          <t>52749</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>82331</t>
+          <t>81890</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,85%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>145547</t>
+          <t>146092</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>166175</t>
+          <t>166123</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>76,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>159081</t>
+          <t>159039</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>180243</t>
+          <t>179141</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>310385</t>
+          <t>310826</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>340881</t>
+          <t>339967</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>79,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>86,57%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>43562</t>
+          <t>44017</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>75284</t>
+          <t>75294</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45679</t>
+          <t>47202</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>73595</t>
+          <t>73984</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>98842</t>
+          <t>99270</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>141046</t>
+          <t>139759</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,42%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>334472</t>
+          <t>334462</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>366194</t>
+          <t>365739</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>367606</t>
+          <t>367217</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>395522</t>
+          <t>393999</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>709911</t>
+          <t>711198</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>752115</t>
+          <t>751687</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>88,33%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22593</t>
+          <t>21675</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42346</t>
+          <t>43092</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>55144</t>
+          <t>55001</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>82655</t>
+          <t>83598</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>80362</t>
+          <t>82530</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>117667</t>
+          <t>117968</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,46%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>194191</t>
+          <t>193445</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>213944</t>
+          <t>214862</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>81,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>206151</t>
+          <t>205208</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>233662</t>
+          <t>233805</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>80,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>407676</t>
+          <t>407375</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>444981</t>
+          <t>442813</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>84,29%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>32406</t>
+          <t>32593</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>56069</t>
+          <t>55465</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>53617</t>
+          <t>52760</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>82241</t>
+          <t>81437</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>93595</t>
+          <t>94248</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>130775</t>
+          <t>130104</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>22,94%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>211462</t>
+          <t>212066</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>235125</t>
+          <t>234938</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>79,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>217293</t>
+          <t>218097</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>245917</t>
+          <t>246774</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>72,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>436290</t>
+          <t>436961</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>473470</t>
+          <t>472817</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>77,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>83,38%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8557</t>
+          <t>8847</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23024</t>
+          <t>23506</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15696</t>
+          <t>15365</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33399</t>
+          <t>33706</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>27925</t>
+          <t>27788</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>51695</t>
+          <t>50567</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>14,69%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>147254</t>
+          <t>146772</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>161721</t>
+          <t>161431</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>140507</t>
+          <t>140200</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>158210</t>
+          <t>158541</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,8%</t>
+          <t>80,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>292489</t>
+          <t>293617</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>316259</t>
+          <t>316396</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>85,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,93%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>27186</t>
+          <t>27729</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>47159</t>
+          <t>50550</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>23482</t>
+          <t>22430</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>44253</t>
+          <t>44094</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>55285</t>
+          <t>55319</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>84982</t>
+          <t>84013</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,34%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>142111</t>
+          <t>138720</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>162084</t>
+          <t>161541</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,08%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>160235</t>
+          <t>160394</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>181006</t>
+          <t>182058</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>78,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>308776</t>
+          <t>309745</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>338473</t>
+          <t>338439</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>85,95%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>56844</t>
+          <t>57638</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>88664</t>
+          <t>88150</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>65839</t>
+          <t>65623</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>100344</t>
+          <t>98779</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>132203</t>
+          <t>131464</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>179212</t>
+          <t>174612</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,4%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>375661</t>
+          <t>376175</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>407481</t>
+          <t>406687</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>81,02%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>439024</t>
+          <t>440589</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>473529</t>
+          <t>473745</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>81,69%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>824480</t>
+          <t>829080</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>871489</t>
+          <t>872228</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>86,9%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>31511</t>
+          <t>30995</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>58281</t>
+          <t>57610</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>63471</t>
+          <t>62138</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>96882</t>
+          <t>95400</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>101670</t>
+          <t>102225</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>144530</t>
+          <t>144415</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,92%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>467271</t>
+          <t>467942</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>494041</t>
+          <t>494557</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>495530</t>
+          <t>497012</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>528941</t>
+          <t>530274</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>973433</t>
+          <t>973548</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1016293</t>
+          <t>1015738</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>90,86%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>303299</t>
+          <t>299928</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>369199</t>
+          <t>369344</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>406123</t>
+          <t>403825</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>483010</t>
+          <t>477766</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>726894</t>
+          <t>722756</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>827500</t>
+          <t>825630</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,89%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2085543</t>
+          <t>2085398</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2151443</t>
+          <t>2154814</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2257927</t>
+          <t>2263171</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2334814</t>
+          <t>2337112</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>82,57%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4368179</t>
+          <t>4370049</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4468785</t>
+          <t>4472923</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>86,09%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26987</t>
+          <t>27034</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>52426</t>
+          <t>54100</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28405</t>
+          <t>27887</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>51322</t>
+          <t>52952</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>60452</t>
+          <t>60590</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>96555</t>
+          <t>98884</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,78%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>198134</t>
+          <t>196460</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>223573</t>
+          <t>223526</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>78,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>197917</t>
+          <t>196287</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>220834</t>
+          <t>221352</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,41%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>403245</t>
+          <t>400916</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>439348</t>
+          <t>439210</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>80,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>87,88%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33768</t>
+          <t>33332</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>62876</t>
+          <t>60623</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>54294</t>
+          <t>55461</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>86455</t>
+          <t>87682</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>98112</t>
+          <t>97541</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>139717</t>
+          <t>140503</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,64%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>343454</t>
+          <t>345707</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>372562</t>
+          <t>372998</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>85,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>351368</t>
+          <t>350141</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>383529</t>
+          <t>382362</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>79,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>704436</t>
+          <t>703650</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>746041</t>
+          <t>746612</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>88,45%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>37367</t>
+          <t>36967</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>64163</t>
+          <t>62839</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>61082</t>
+          <t>62434</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>92690</t>
+          <t>95390</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>105124</t>
+          <t>106627</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>145955</t>
+          <t>149968</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>24,09%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>229501</t>
+          <t>230825</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>256297</t>
+          <t>256697</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>78,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>87,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>236062</t>
+          <t>233362</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>267670</t>
+          <t>266318</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>70,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>81,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>476461</t>
+          <t>472448</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>517292</t>
+          <t>515789</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,55%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>82,87%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>33884</t>
+          <t>33341</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>58325</t>
+          <t>58898</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>46855</t>
+          <t>46583</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>75296</t>
+          <t>74600</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>85638</t>
+          <t>86842</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>122558</t>
+          <t>126460</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>19,28%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>254752</t>
+          <t>254179</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>279193</t>
+          <t>279736</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>81,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>267519</t>
+          <t>268215</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>295960</t>
+          <t>296232</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>78,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>533333</t>
+          <t>529431</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>570253</t>
+          <t>569049</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,31%</t>
+          <t>80,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>86,76%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23303</t>
+          <t>22965</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>46551</t>
+          <t>43991</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>23901</t>
+          <t>24920</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>45844</t>
+          <t>45583</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>54006</t>
+          <t>53741</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>84468</t>
+          <t>84017</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,73%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>145507</t>
+          <t>148067</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>168755</t>
+          <t>169093</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>77,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>148738</t>
+          <t>148999</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>170681</t>
+          <t>169662</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,44%</t>
+          <t>76,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>302172</t>
+          <t>302623</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>332634</t>
+          <t>332899</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>78,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>86,1%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20337</t>
+          <t>19853</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>39843</t>
+          <t>40506</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>40064</t>
+          <t>43029</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>67464</t>
+          <t>67626</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>69020</t>
+          <t>69406</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>101481</t>
+          <t>100367</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,5%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>210130</t>
+          <t>209467</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>229636</t>
+          <t>230120</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>197366</t>
+          <t>197204</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>224766</t>
+          <t>221801</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>74,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>413322</t>
+          <t>414436</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>445783</t>
+          <t>445397</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>86,52%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>94749</t>
+          <t>93326</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>136249</t>
+          <t>134689</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>110637</t>
+          <t>111461</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>153097</t>
+          <t>154041</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>217591</t>
+          <t>217214</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>275236</t>
+          <t>276862</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>23,05%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>438842</t>
+          <t>440402</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>480342</t>
+          <t>481765</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>472890</t>
+          <t>471946</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>515350</t>
+          <t>514526</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>75,54%</t>
+          <t>75,39%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>925842</t>
+          <t>924216</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>983487</t>
+          <t>983864</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>76,95%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>81,88%</t>
+          <t>81,92%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>64664</t>
+          <t>65892</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>100117</t>
+          <t>100307</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>91854</t>
+          <t>90701</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>130798</t>
+          <t>130593</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>164690</t>
+          <t>163788</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>219077</t>
+          <t>218765</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,37%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>533788</t>
+          <t>533598</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>569241</t>
+          <t>568013</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>84,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>571496</t>
+          <t>571701</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>610440</t>
+          <t>611593</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1117122</t>
+          <t>1117434</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1171509</t>
+          <t>1172411</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,63%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>87,74%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>400015</t>
+          <t>400853</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>479745</t>
+          <t>482157</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>529515</t>
+          <t>526808</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>620549</t>
+          <t>614330</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>952121</t>
+          <t>949783</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1068420</t>
+          <t>1070834</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,67%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2434914</t>
+          <t>2432502</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2514644</t>
+          <t>2513806</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>83,46%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2525772</t>
+          <t>2531991</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2616806</t>
+          <t>2619513</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>80,28%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4992560</t>
+          <t>4990146</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5108859</t>
+          <t>5111197</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>84,33%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6814</t>
+          <t>6849</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20996</t>
+          <t>22189</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11959</t>
+          <t>12649</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29337</t>
+          <t>29503</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21578</t>
+          <t>22770</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46879</t>
+          <t>44816</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,12%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>224222</t>
+          <t>223029</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>238404</t>
+          <t>238369</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>216997</t>
+          <t>216831</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>234375</t>
+          <t>233685</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>444672</t>
+          <t>446735</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>469973</t>
+          <t>468781</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,37%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38289</t>
+          <t>36983</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>64477</t>
+          <t>65035</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45913</t>
+          <t>45185</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>75035</t>
+          <t>74363</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>89555</t>
+          <t>88947</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>128028</t>
+          <t>128587</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>17,0%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>298688</t>
+          <t>298130</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>324876</t>
+          <t>326182</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>82,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>318292</t>
+          <t>318964</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>347414</t>
+          <t>348142</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>628464</t>
+          <t>627905</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>666937</t>
+          <t>667545</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,24%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21326</t>
+          <t>23105</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>43411</t>
+          <t>44534</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20648</t>
+          <t>21129</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42662</t>
+          <t>42638</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>49009</t>
+          <t>48884</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>80376</t>
+          <t>77485</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>12,95%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>247096</t>
+          <t>245973</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>269181</t>
+          <t>267402</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>265102</t>
+          <t>265126</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>287116</t>
+          <t>286635</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>517894</t>
+          <t>520785</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>549261</t>
+          <t>549386</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>87,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,83%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31697</t>
+          <t>31767</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>57502</t>
+          <t>58006</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>42738</t>
+          <t>43624</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>73243</t>
+          <t>73795</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>81913</t>
+          <t>83354</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>120472</t>
+          <t>122445</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>18,04%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>272545</t>
+          <t>272041</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>298350</t>
+          <t>298280</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>82,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>275618</t>
+          <t>275066</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>306123</t>
+          <t>305237</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,01%</t>
+          <t>78,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>558436</t>
+          <t>556463</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>596995</t>
+          <t>595554</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,72%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10600</t>
+          <t>10681</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26471</t>
+          <t>26566</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17184</t>
+          <t>17544</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>34733</t>
+          <t>34544</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31856</t>
+          <t>32855</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>57117</t>
+          <t>55255</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>20,87%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>92751</t>
+          <t>92656</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>108622</t>
+          <t>108541</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,8%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>110767</t>
+          <t>110956</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>128316</t>
+          <t>127956</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>207605</t>
+          <t>209467</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>232866</t>
+          <t>231867</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>87,59%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10284</t>
+          <t>9900</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25575</t>
+          <t>25545</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9273</t>
+          <t>9149</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26048</t>
+          <t>26314</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>23268</t>
+          <t>22973</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>46053</t>
+          <t>46036</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,7 +9179,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>208040</t>
+          <t>208070</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>223331</t>
+          <t>223715</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>221089</t>
+          <t>220823</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>237864</t>
+          <t>237988</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>434700</t>
+          <t>434717</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>457485</t>
+          <t>457780</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9297,7 +9297,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,22%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25931</t>
+          <t>26854</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>50841</t>
+          <t>50410</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>32312</t>
+          <t>31502</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>57707</t>
+          <t>57070</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>62265</t>
+          <t>64155</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>98417</t>
+          <t>99053</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,66%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>391466</t>
+          <t>391897</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>416376</t>
+          <t>415453</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>429344</t>
+          <t>429981</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>454739</t>
+          <t>455549</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>830941</t>
+          <t>830305</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>867093</t>
+          <t>865203</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,1%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>60380</t>
+          <t>61464</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>93776</t>
+          <t>96352</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>66913</t>
+          <t>66604</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>103872</t>
+          <t>100944</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>134326</t>
+          <t>134880</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>185021</t>
+          <t>184857</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,88%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>546476</t>
+          <t>543900</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>579872</t>
+          <t>578788</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>587469</t>
+          <t>590397</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>624428</t>
+          <t>624737</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>85,4%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1146572</t>
+          <t>1146736</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1197267</t>
+          <t>1196713</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>89,87%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>253386</t>
+          <t>254844</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>318699</t>
+          <t>317446</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>296557</t>
+          <t>298011</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>369711</t>
+          <t>372425</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>570141</t>
+          <t>574241</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>667864</t>
+          <t>672027</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,15%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2345634</t>
+          <t>2346887</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2410947</t>
+          <t>2409489</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2497604</t>
+          <t>2494890</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2570758</t>
+          <t>2569304</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4863784</t>
+          <t>4859621</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4961507</t>
+          <t>4957407</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,62%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>29337</t>
+          <t>31377</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20615</t>
+          <t>23191</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41271</t>
+          <t>42159</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>22683</t>
+          <t>22875</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16786</t>
+          <t>16542</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30673</t>
+          <t>30163</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>52021</t>
+          <t>54252</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>40552</t>
+          <t>43328</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>64744</t>
+          <t>66457</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,89%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>276093</t>
+          <t>269540</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>264159</t>
+          <t>258758</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>284815</t>
+          <t>277726</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>85,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>264924</t>
+          <t>286589</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>256934</t>
+          <t>279301</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>270821</t>
+          <t>292922</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>541016</t>
+          <t>556129</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>528293</t>
+          <t>543924</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>552485</t>
+          <t>567053</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>92,9%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>305430</t>
+          <t>300917</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>305430</t>
+          <t>300917</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>305430</t>
+          <t>300917</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>287607</t>
+          <t>309464</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>287607</t>
+          <t>309464</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>287607</t>
+          <t>309464</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>593037</t>
+          <t>610381</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>593037</t>
+          <t>610381</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>593037</t>
+          <t>610381</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>38287</t>
+          <t>41977</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27656</t>
+          <t>30368</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>51814</t>
+          <t>55324</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>65965</t>
+          <t>70539</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>54744</t>
+          <t>57848</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>78072</t>
+          <t>83617</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>104252</t>
+          <t>112515</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>87761</t>
+          <t>94908</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>122800</t>
+          <t>132179</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,59%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>468697</t>
+          <t>476051</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>455170</t>
+          <t>462704</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>479328</t>
+          <t>487660</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>435583</t>
+          <t>461073</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>423476</t>
+          <t>447995</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>446804</t>
+          <t>473764</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>904280</t>
+          <t>937125</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>885732</t>
+          <t>917461</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>920771</t>
+          <t>954732</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>90,96%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>506984</t>
+          <t>518028</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>506984</t>
+          <t>518028</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>506984</t>
+          <t>518028</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>501548</t>
+          <t>531612</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>501548</t>
+          <t>531612</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>501548</t>
+          <t>531612</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1008532</t>
+          <t>1049640</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1008532</t>
+          <t>1049640</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1008532</t>
+          <t>1049640</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,27 +11383,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>34330</t>
+          <t>33897</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26096</t>
+          <t>26334</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44119</t>
+          <t>43986</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>49015</t>
+          <t>50369</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>39827</t>
+          <t>40793</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59434</t>
+          <t>61136</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>83345</t>
+          <t>84266</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>70490</t>
+          <t>71220</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>98076</t>
+          <t>97492</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,19%</t>
         </is>
       </c>
     </row>
@@ -11496,22 +11496,22 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>266862</t>
+          <t>266334</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>257073</t>
+          <t>256245</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>275096</t>
+          <t>273897</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -11521,7 +11521,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>286260</t>
+          <t>291336</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>275841</t>
+          <t>280569</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>295448</t>
+          <t>300912</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>553122</t>
+          <t>557669</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>538391</t>
+          <t>544443</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>565977</t>
+          <t>570715</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>86,87%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>88,91%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>301192</t>
+          <t>300231</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>301192</t>
+          <t>300231</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>301192</t>
+          <t>300231</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>335275</t>
+          <t>341705</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>335275</t>
+          <t>341705</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>335275</t>
+          <t>341705</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>636467</t>
+          <t>641935</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>636467</t>
+          <t>641935</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>636467</t>
+          <t>641935</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>37794</t>
+          <t>43399</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28013</t>
+          <t>32399</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>51095</t>
+          <t>59601</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>48686</t>
+          <t>52505</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30828</t>
+          <t>43091</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>63910</t>
+          <t>63701</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>86480</t>
+          <t>95904</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>64561</t>
+          <t>79151</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>106518</t>
+          <t>114666</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>14,51%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>272326</t>
+          <t>327339</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>259025</t>
+          <t>311137</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>282107</t>
+          <t>338339</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>424779</t>
+          <t>367108</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>409555</t>
+          <t>355912</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>442637</t>
+          <t>376522</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>87,49%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>697105</t>
+          <t>694447</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>677067</t>
+          <t>675685</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>719024</t>
+          <t>711200</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>89,99%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>310120</t>
+          <t>370738</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>310120</t>
+          <t>370738</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>310120</t>
+          <t>370738</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>473465</t>
+          <t>419613</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>473465</t>
+          <t>419613</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>473465</t>
+          <t>419613</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>783585</t>
+          <t>790351</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>783585</t>
+          <t>790351</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>783585</t>
+          <t>790351</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>18853</t>
+          <t>19814</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13370</t>
+          <t>13585</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25537</t>
+          <t>26762</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>42651</t>
+          <t>44433</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>36102</t>
+          <t>37585</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>50363</t>
+          <t>52171</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>61504</t>
+          <t>64247</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>52390</t>
+          <t>55438</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>73062</t>
+          <t>76116</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>18,61%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>149576</t>
+          <t>169485</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>142892</t>
+          <t>162537</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>155059</t>
+          <t>175714</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>85,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>159641</t>
+          <t>175369</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>151929</t>
+          <t>167631</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>166190</t>
+          <t>182217</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>79,79%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>309217</t>
+          <t>344854</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>297659</t>
+          <t>332985</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>318331</t>
+          <t>353663</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>83,41%</t>
+          <t>84,3%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>86,45%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>168429</t>
+          <t>189299</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>168429</t>
+          <t>189299</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>168429</t>
+          <t>189299</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>202292</t>
+          <t>219802</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>202292</t>
+          <t>219802</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>202292</t>
+          <t>219802</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>370721</t>
+          <t>409101</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>370721</t>
+          <t>409101</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>370721</t>
+          <t>409101</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>32214</t>
+          <t>32163</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>25156</t>
+          <t>24520</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>41267</t>
+          <t>41652</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>27443</t>
+          <t>27757</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21587</t>
+          <t>21245</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34847</t>
+          <t>35429</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>59658</t>
+          <t>59920</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>48941</t>
+          <t>50576</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>70617</t>
+          <t>70219</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,01%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>221518</t>
+          <t>217572</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>212465</t>
+          <t>208083</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>228576</t>
+          <t>225215</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>218907</t>
+          <t>223803</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>211503</t>
+          <t>216131</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>224763</t>
+          <t>230315</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>440424</t>
+          <t>441374</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>429465</t>
+          <t>431075</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>451141</t>
+          <t>450718</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>85,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>89,91%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>253732</t>
+          <t>249735</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>253732</t>
+          <t>249735</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>253732</t>
+          <t>249735</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>246350</t>
+          <t>251560</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>246350</t>
+          <t>251560</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>246350</t>
+          <t>251560</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>500082</t>
+          <t>501294</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>500082</t>
+          <t>501294</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>500082</t>
+          <t>501294</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>75453</t>
+          <t>89747</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>59384</t>
+          <t>71374</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>94391</t>
+          <t>110135</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>74969</t>
+          <t>93179</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>32434</t>
+          <t>77958</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>105539</t>
+          <t>111652</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>150422</t>
+          <t>182926</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>87121</t>
+          <t>158565</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>187095</t>
+          <t>209769</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>14,58%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>524242</t>
+          <t>607933</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>505304</t>
+          <t>587545</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>540311</t>
+          <t>626306</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>84,26%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>753396</t>
+          <t>648207</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>722826</t>
+          <t>629734</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>795931</t>
+          <t>663428</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1277638</t>
+          <t>1256140</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1240965</t>
+          <t>1229297</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1340939</t>
+          <t>1280501</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>87,29%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>88,98%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>599695</t>
+          <t>697680</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>599695</t>
+          <t>697680</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>599695</t>
+          <t>697680</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>828365</t>
+          <t>741386</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>828365</t>
+          <t>741386</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>828365</t>
+          <t>741386</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1428060</t>
+          <t>1439066</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1428060</t>
+          <t>1439066</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1428060</t>
+          <t>1439066</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>54347</t>
+          <t>59966</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>25395</t>
+          <t>47094</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>78796</t>
+          <t>74521</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>66517</t>
+          <t>75876</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>54867</t>
+          <t>62112</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>79113</t>
+          <t>90079</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>120864</t>
+          <t>135841</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>74538</t>
+          <t>116454</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>148241</t>
+          <t>155667</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,84%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>854292</t>
+          <t>711084</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>829843</t>
+          <t>696529</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>883244</t>
+          <t>723956</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>637407</t>
+          <t>734431</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>624811</t>
+          <t>720228</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>649057</t>
+          <t>748195</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1491699</t>
+          <t>1445516</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1464322</t>
+          <t>1425690</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1538025</t>
+          <t>1464903</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>92,64%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>908639</t>
+          <t>771050</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>908639</t>
+          <t>771050</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>908639</t>
+          <t>771050</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>703924</t>
+          <t>810307</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>703924</t>
+          <t>810307</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>703924</t>
+          <t>810307</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1612563</t>
+          <t>1581357</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1612563</t>
+          <t>1581357</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1612563</t>
+          <t>1581357</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>320615</t>
+          <t>352339</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>247443</t>
+          <t>318270</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>360860</t>
+          <t>390567</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>397930</t>
+          <t>437533</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>326155</t>
+          <t>410127</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>438160</t>
+          <t>473377</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>718545</t>
+          <t>789872</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>622322</t>
+          <t>746058</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>779952</t>
+          <t>843528</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>12,01%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3033606</t>
+          <t>3045339</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2993361</t>
+          <t>3007111</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3106778</t>
+          <t>3079408</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3180897</t>
+          <t>3187915</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3140667</t>
+          <t>3152071</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3252672</t>
+          <t>3215321</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>86,94%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6214503</t>
+          <t>6233253</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6153096</t>
+          <t>6179597</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6310726</t>
+          <t>6277067</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>89,38%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3354221</t>
+          <t>3397678</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3354221</t>
+          <t>3397678</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3354221</t>
+          <t>3397678</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3578827</t>
+          <t>3625448</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3578827</t>
+          <t>3625448</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3578827</t>
+          <t>3625448</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>6933048</t>
+          <t>7023125</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>6933048</t>
+          <t>7023125</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>6933048</t>
+          <t>7023125</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
